--- a/arista/dist/20261025_Arista模型_v0.2.1.xlsx
+++ b/arista/dist/20261025_Arista模型_v0.2.1.xlsx
@@ -6081,7 +6081,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6318,7 +6318,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6439,7 +6439,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6560,7 +6560,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6681,7 +6681,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6802,7 +6802,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/arista/dist/20261025_Arista模型_v0.2.1.xlsx
+++ b/arista/dist/20261025_Arista模型_v0.2.1.xlsx
@@ -5441,7 +5441,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5460,7 +5460,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5774,7 +5774,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5793,7 +5793,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/arista/dist/20261025_Arista模型_v0.2.1.xlsx
+++ b/arista/dist/20261025_Arista模型_v0.2.1.xlsx
@@ -6062,26 +6062,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6299,26 +6299,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6420,26 +6420,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6541,26 +6541,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6662,26 +6662,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6783,26 +6783,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -32699,7 +32699,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>34</v>
